--- a/output_data/stress_response_phylum.xlsx
+++ b/output_data/stress_response_phylum.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="20" windowWidth="16100" windowHeight="9660" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -544,9 +544,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,7 +560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -574,7 +574,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -588,7 +588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -602,7 +602,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -616,7 +616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -630,7 +630,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -644,7 +644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -658,7 +658,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -672,7 +672,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -686,7 +686,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -700,7 +700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -714,7 +714,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -728,7 +728,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -742,7 +742,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -756,7 +756,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -770,7 +770,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -784,7 +784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -798,7 +798,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -812,7 +812,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -826,7 +826,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -840,7 +840,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -854,7 +854,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -868,7 +868,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -882,7 +882,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -896,7 +896,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -910,7 +910,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -924,7 +924,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -938,7 +938,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -952,7 +952,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -966,7 +966,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -980,7 +980,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -994,7 +994,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -1170,13 +1170,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.453125" customWidth="1"/>
-    <col min="2" max="2" width="26.90625" customWidth="1"/>
+    <col min="1" max="1" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1184,31 +1184,31 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1232,127 +1232,127 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -1360,55 +1360,55 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -1416,55 +1416,55 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B31" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>46</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -1529,8 +1529,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:B44">
-    <sortCondition ref="B2:B44"/>
+  <sortState ref="A2:A44">
+    <sortCondition ref="A2:A44"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
